--- a/03_Outputs/all/03_DS/ds_idx1_servicio.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx1_servicio.xlsx
@@ -393,13 +393,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.5677041981028235</v>
+        <v>0.5677041981028239</v>
       </c>
       <c r="D2">
-        <v>0.858278237558002</v>
+        <v>0.8582782375580027</v>
       </c>
       <c r="E2">
-        <v>-0.08819811845241342</v>
+        <v>-0.0881981184524136</v>
       </c>
     </row>
     <row r="3">
@@ -414,13 +414,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.5049654193415246</v>
+        <v>0.5049654193415247</v>
       </c>
       <c r="D3">
-        <v>0.1341521741395288</v>
+        <v>0.1341521741395292</v>
       </c>
       <c r="E3">
-        <v>0.1335014893141037</v>
+        <v>0.1335014893141034</v>
       </c>
     </row>
     <row r="4">
@@ -438,10 +438,10 @@
         <v>-0.8298084167992978</v>
       </c>
       <c r="D4">
-        <v>0.4794444667456806</v>
+        <v>0.4794444667456811</v>
       </c>
       <c r="E4">
-        <v>0.2045763110614249</v>
+        <v>0.2045763110614248</v>
       </c>
     </row>
     <row r="5">
@@ -459,10 +459,10 @@
         <v>0.4636837543062415</v>
       </c>
       <c r="D5">
-        <v>0.1448313172098222</v>
+        <v>0.1448313172098225</v>
       </c>
       <c r="E5">
-        <v>0.135699679677423</v>
+        <v>0.1356996796774226</v>
       </c>
     </row>
     <row r="6">
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>-2.965998336880667</v>
+        <v>-2.965998336880666</v>
       </c>
       <c r="D6">
-        <v>-1.547942167030894</v>
+        <v>-1.547942167030893</v>
       </c>
       <c r="E6">
         <v>-2.425425185199579</v>
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D7">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E7">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="8">
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.7239438588581674</v>
+        <v>0.7239438588581677</v>
       </c>
       <c r="D8">
-        <v>0.9467294718961333</v>
+        <v>0.946729471896134</v>
       </c>
       <c r="E8">
-        <v>-0.09301633008136674</v>
+        <v>-0.09301633008136695</v>
       </c>
     </row>
     <row r="9">
@@ -540,13 +540,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>-1.410795821115399</v>
+        <v>-1.4107958211154</v>
       </c>
       <c r="D9">
         <v>-1.642647104629121</v>
       </c>
       <c r="E9">
-        <v>-0.8233556639411005</v>
+        <v>-0.8233556639411008</v>
       </c>
     </row>
     <row r="10">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.2978320642206242</v>
+        <v>-0.297832064220624</v>
       </c>
       <c r="D10">
-        <v>-0.1196479315991166</v>
+        <v>-0.119647931599116</v>
       </c>
       <c r="E10">
-        <v>-0.6239972066354978</v>
+        <v>-0.6239972066354981</v>
       </c>
     </row>
     <row r="11">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C11">
-        <v>0.7308887415838913</v>
+        <v>0.7308887415838916</v>
       </c>
       <c r="D11">
-        <v>0.9081827556544864</v>
+        <v>0.908182755654487</v>
       </c>
       <c r="E11">
-        <v>-0.09856838280264214</v>
+        <v>-0.09856838280264232</v>
       </c>
     </row>
     <row r="12">
@@ -603,13 +603,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.3894147138719495</v>
+        <v>0.3894147138719498</v>
       </c>
       <c r="D12">
-        <v>0.4276212700731006</v>
+        <v>0.4276212700731011</v>
       </c>
       <c r="E12">
-        <v>-0.2046198197230021</v>
+        <v>-0.2046198197230022</v>
       </c>
     </row>
     <row r="13">
@@ -627,10 +627,10 @@
         <v>-1.726105175593315</v>
       </c>
       <c r="D13">
-        <v>-2.483048684977205</v>
+        <v>-2.483048684977206</v>
       </c>
       <c r="E13">
-        <v>-0.2503058035649424</v>
+        <v>-0.2503058035649426</v>
       </c>
     </row>
     <row r="14">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.7724647241134329</v>
+        <v>0.7724647241134333</v>
       </c>
       <c r="D14">
-        <v>0.9322440889339887</v>
+        <v>0.9322440889339894</v>
       </c>
       <c r="E14">
-        <v>-0.1023930276848192</v>
+        <v>-0.1023930276848194</v>
       </c>
     </row>
     <row r="15">
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="C15">
-        <v>0.4499231992944803</v>
+        <v>0.4499231992944805</v>
       </c>
       <c r="D15">
-        <v>0.1483910315665866</v>
+        <v>0.148391031566587</v>
       </c>
       <c r="E15">
-        <v>0.1364324097985293</v>
+        <v>0.136432409798529</v>
       </c>
     </row>
     <row r="16">
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.6616624385911406</v>
+        <v>0.6616624385911409</v>
       </c>
       <c r="D16">
-        <v>0.9647745692150425</v>
+        <v>0.964774569215043</v>
       </c>
       <c r="E16">
-        <v>-0.08290690235680788</v>
+        <v>-0.08290690235680803</v>
       </c>
     </row>
     <row r="17">
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D17">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E17">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="18">
@@ -732,10 +732,10 @@
         <v>-0.7304841984783123</v>
       </c>
       <c r="D18">
-        <v>-1.066731669727173</v>
+        <v>-1.066731669727172</v>
       </c>
       <c r="E18">
-        <v>-0.5416406793169416</v>
+        <v>-0.5416406793169418</v>
       </c>
     </row>
     <row r="19">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.02585174161807387</v>
+        <v>-0.0258517416180738</v>
       </c>
       <c r="D19">
-        <v>-0.3614780969435564</v>
+        <v>-0.361478096943556</v>
       </c>
       <c r="E19">
-        <v>-0.1720011481973218</v>
+        <v>-0.1720011481973221</v>
       </c>
     </row>
     <row r="20">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D20">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E20">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="21">
@@ -792,13 +792,13 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.3823869332765135</v>
+        <v>0.3823869332765137</v>
       </c>
       <c r="D21">
-        <v>0.5118903040617953</v>
+        <v>0.5118903040617958</v>
       </c>
       <c r="E21">
-        <v>-0.2398916684573011</v>
+        <v>-0.2398916684573013</v>
       </c>
     </row>
     <row r="22">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.3495694283779265</v>
+        <v>0.3495694283779267</v>
       </c>
       <c r="D22">
-        <v>0.2304760523190972</v>
+        <v>0.2304760523190977</v>
       </c>
       <c r="E22">
-        <v>-0.1567673159694408</v>
+        <v>-0.156767315969441</v>
       </c>
     </row>
     <row r="23">
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.175629628135332</v>
+        <v>0.1756296281353321</v>
       </c>
       <c r="D23">
-        <v>0.1688197665140226</v>
+        <v>0.168819766514023</v>
       </c>
       <c r="E23">
-        <v>0.1129412338819087</v>
+        <v>0.1129412338819084</v>
       </c>
     </row>
     <row r="24">
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.119669879012215</v>
+        <v>0.1196698790122151</v>
       </c>
       <c r="D24">
-        <v>0.2338241761289335</v>
+        <v>0.2338241761289338</v>
       </c>
       <c r="E24">
-        <v>0.154017932705083</v>
+        <v>0.1540179327050828</v>
       </c>
     </row>
     <row r="25">
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.353599314212153</v>
+        <v>0.3535993142121531</v>
       </c>
       <c r="D25">
-        <v>0.1733090320639378</v>
+        <v>0.1733090320639381</v>
       </c>
       <c r="E25">
-        <v>0.1415615206462741</v>
+        <v>0.1415615206462738</v>
       </c>
     </row>
     <row r="26">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="C26">
-        <v>-0.141284484318324</v>
+        <v>-0.1412844843183245</v>
       </c>
       <c r="D26">
-        <v>-1.782135158976793</v>
+        <v>-1.782135158976794</v>
       </c>
       <c r="E26">
-        <v>0.5473466094551821</v>
+        <v>0.5473466094551815</v>
       </c>
     </row>
     <row r="27">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.2065104568976403</v>
+        <v>-0.2065104568976407</v>
       </c>
       <c r="D27">
         <v>-1.712057165215</v>
       </c>
       <c r="E27">
-        <v>0.4279148181511948</v>
+        <v>0.4279148181511943</v>
       </c>
     </row>
     <row r="28">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.6009459196202084</v>
+        <v>0.6009459196202088</v>
       </c>
       <c r="D28">
-        <v>0.9011804175535456</v>
+        <v>0.9011804175535463</v>
       </c>
       <c r="E28">
-        <v>-0.1104174186720137</v>
+        <v>-0.1104174186720138</v>
       </c>
     </row>
     <row r="29">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.5600076393885688</v>
+        <v>0.5600076393885689</v>
       </c>
       <c r="D29">
-        <v>0.119913316712471</v>
+        <v>0.1199133167124713</v>
       </c>
       <c r="E29">
-        <v>0.1305705688296781</v>
+        <v>0.1305705688296778</v>
       </c>
     </row>
     <row r="30">
@@ -981,13 +981,13 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D30">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E30">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="31">
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.5324865293650467</v>
+        <v>0.5324865293650468</v>
       </c>
       <c r="D31">
-        <v>0.1270327454259999</v>
+        <v>0.1270327454260002</v>
       </c>
       <c r="E31">
-        <v>0.1320360290718909</v>
+        <v>0.1320360290718905</v>
       </c>
     </row>
     <row r="32">
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="C32">
-        <v>-1.137245145086052</v>
+        <v>-1.137245145086053</v>
       </c>
       <c r="D32">
-        <v>-2.827634604936395</v>
+        <v>-2.827634604936396</v>
       </c>
       <c r="E32">
-        <v>0.08082045401489088</v>
+        <v>0.08082045401489035</v>
       </c>
     </row>
     <row r="33">
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.4912048643297636</v>
+        <v>0.4912048643297637</v>
       </c>
       <c r="D33">
-        <v>0.1377118884962933</v>
+        <v>0.1377118884962936</v>
       </c>
       <c r="E33">
-        <v>0.1342342194352101</v>
+        <v>0.1342342194352098</v>
       </c>
     </row>
     <row r="34">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.4821362584668755</v>
+        <v>0.4821362584668759</v>
       </c>
       <c r="D34">
-        <v>0.6952291757935227</v>
+        <v>0.6952291757935235</v>
       </c>
       <c r="E34">
-        <v>-0.269504410997227</v>
+        <v>-0.2695044109972272</v>
       </c>
     </row>
     <row r="35">
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D35">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E35">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="36">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.5462470843768077</v>
+        <v>0.5462470843768078</v>
       </c>
       <c r="D36">
-        <v>0.1234730310692355</v>
+        <v>0.1234730310692358</v>
       </c>
       <c r="E36">
-        <v>0.1313032989507845</v>
+        <v>0.1313032989507841</v>
       </c>
     </row>
     <row r="37">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D37">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E37">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="38">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="C38">
-        <v>-5.687284335950952</v>
+        <v>-5.687284335950951</v>
       </c>
       <c r="D38">
-        <v>1.736023634683532</v>
+        <v>1.736023634683533</v>
       </c>
       <c r="E38">
-        <v>0.4632300438119852</v>
+        <v>0.463230043811986</v>
       </c>
     </row>
     <row r="39">
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.4229631775451228</v>
+        <v>0.4229631775451231</v>
       </c>
       <c r="D39">
-        <v>0.4327206773057778</v>
+        <v>0.4327206773057783</v>
       </c>
       <c r="E39">
-        <v>-0.1734915543477416</v>
+        <v>-0.1734915543477418</v>
       </c>
     </row>
     <row r="40">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="C40">
-        <v>0.4774443093180025</v>
+        <v>0.4774443093180026</v>
       </c>
       <c r="D40">
-        <v>0.1412716028530577</v>
+        <v>0.1412716028530581</v>
       </c>
       <c r="E40">
-        <v>0.1349669495563165</v>
+        <v>0.1349669495563162</v>
       </c>
     </row>
     <row r="41">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D41">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E41">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="42">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.2825547102164395</v>
+        <v>0.2825547102164397</v>
       </c>
       <c r="D42">
-        <v>0.3742737500771154</v>
+        <v>0.374273750077116</v>
       </c>
       <c r="E42">
-        <v>-0.2511028273729496</v>
+        <v>-0.2511028273729498</v>
       </c>
     </row>
     <row r="43">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="C43">
-        <v>0.5187259743532856</v>
+        <v>0.5187259743532857</v>
       </c>
       <c r="D43">
-        <v>0.1305924597827644</v>
+        <v>0.1305924597827647</v>
       </c>
       <c r="E43">
-        <v>0.1327687591929973</v>
+        <v>0.1327687591929969</v>
       </c>
     </row>
     <row r="44">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="C44">
-        <v>-0.6702722396350169</v>
+        <v>-0.6702722396350178</v>
       </c>
       <c r="D44">
-        <v>-2.831476477465257</v>
+        <v>-2.831476477465258</v>
       </c>
       <c r="E44">
-        <v>0.6527611096163271</v>
+        <v>0.6527611096163264</v>
       </c>
     </row>
     <row r="45">
@@ -1299,10 +1299,10 @@
         <v>-1.073145280785643</v>
       </c>
       <c r="D45">
-        <v>-0.9401220239148903</v>
+        <v>-0.94012202391489</v>
       </c>
       <c r="E45">
-        <v>-0.5913948964631763</v>
+        <v>-0.5913948964631766</v>
       </c>
     </row>
     <row r="46">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="C46">
-        <v>-0.3988839380971285</v>
+        <v>-0.3988839380971293</v>
       </c>
       <c r="D46">
-        <v>-2.88042599943812</v>
+        <v>-2.880425999438122</v>
       </c>
       <c r="E46">
-        <v>0.8369187198603257</v>
+        <v>0.836918719860325</v>
       </c>
     </row>
     <row r="47">
@@ -1338,13 +1338,13 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.07504027695602447</v>
+        <v>0.07504027695602464</v>
       </c>
       <c r="D47">
-        <v>0.1158096614245937</v>
+        <v>0.1158096614245941</v>
       </c>
       <c r="E47">
-        <v>-0.174853294030504</v>
+        <v>-0.1748532940305042</v>
       </c>
     </row>
     <row r="48">
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="C48">
-        <v>0.4428450313680719</v>
+        <v>0.4428450313680723</v>
       </c>
       <c r="D48">
-        <v>0.7225518919763506</v>
+        <v>0.7225518919763512</v>
       </c>
       <c r="E48">
-        <v>-0.1916384014992063</v>
+        <v>-0.1916384014992065</v>
       </c>
     </row>
     <row r="49">
@@ -1380,13 +1380,13 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.7587041691016718</v>
+        <v>0.7587041691016722</v>
       </c>
       <c r="D49">
-        <v>0.9358038032907532</v>
+        <v>0.9358038032907537</v>
       </c>
       <c r="E49">
-        <v>-0.1016602975637128</v>
+        <v>-0.101660297563713</v>
       </c>
     </row>
     <row r="50">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.4531717274162317</v>
+        <v>-0.4531717274162326</v>
       </c>
       <c r="D50">
-        <v>-2.888150824805567</v>
+        <v>-2.888150824805568</v>
       </c>
       <c r="E50">
-        <v>0.9182445342181846</v>
+        <v>0.9182445342181839</v>
       </c>
     </row>
     <row r="51">
@@ -1422,13 +1422,13 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.1222903464240005</v>
+        <v>-0.1222903464240007</v>
       </c>
       <c r="D51">
-        <v>-0.9347261173435997</v>
+        <v>-0.9347261173435998</v>
       </c>
       <c r="E51">
-        <v>0.1171820044112731</v>
+        <v>0.1171820044112727</v>
       </c>
     </row>
     <row r="52">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="C52">
-        <v>-0.3019767271265678</v>
+        <v>-0.3019767271265675</v>
       </c>
       <c r="D52">
-        <v>0.07558562153958373</v>
+        <v>0.07558562153958447</v>
       </c>
       <c r="E52">
-        <v>-0.7316950548012813</v>
+        <v>-0.7316950548012814</v>
       </c>
     </row>
     <row r="53">
@@ -1470,7 +1470,7 @@
         <v>1.424224246772744</v>
       </c>
       <c r="E53">
-        <v>0.01806106038494521</v>
+        <v>0.01806106038494543</v>
       </c>
     </row>
     <row r="54">
@@ -1488,10 +1488,10 @@
         <v>0.4224020892709583</v>
       </c>
       <c r="D54">
-        <v>0.1555104602801156</v>
+        <v>0.1555104602801159</v>
       </c>
       <c r="E54">
-        <v>0.1378978700407421</v>
+        <v>0.1378978700407418</v>
       </c>
     </row>
     <row r="55">
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.6276199737758399</v>
+        <v>0.6276199737758402</v>
       </c>
       <c r="D55">
-        <v>0.9716474723934845</v>
+        <v>0.9716474723934851</v>
       </c>
       <c r="E55">
-        <v>-0.08788721923362187</v>
+        <v>-0.08788721923362208</v>
       </c>
     </row>
     <row r="56">
@@ -1527,13 +1527,13 @@
         </is>
       </c>
       <c r="C56">
-        <v>-0.1566886780525927</v>
+        <v>-0.1566886780525924</v>
       </c>
       <c r="D56">
-        <v>0.672868832639808</v>
+        <v>0.6728688326398089</v>
       </c>
       <c r="E56">
-        <v>-0.2749851830285505</v>
+        <v>-0.2749851830285506</v>
       </c>
     </row>
     <row r="57">
@@ -1551,10 +1551,10 @@
         <v>0.1844807309062363</v>
       </c>
       <c r="D57">
-        <v>-0.1441559527081364</v>
+        <v>-0.1441559527081362</v>
       </c>
       <c r="E57">
-        <v>0.08985038793355404</v>
+        <v>0.08985038793355372</v>
       </c>
     </row>
     <row r="58">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="C58">
-        <v>-0.1647596400432897</v>
+        <v>-0.1647596400432901</v>
       </c>
       <c r="D58">
-        <v>-1.589622120471088</v>
+        <v>-1.589622120471089</v>
       </c>
       <c r="E58">
-        <v>0.2896206390619921</v>
+        <v>0.2896206390619916</v>
       </c>
     </row>
     <row r="59">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="C59">
-        <v>-0.02908860271818219</v>
+        <v>-0.0290886027181821</v>
       </c>
       <c r="D59">
-        <v>-0.2071096129807935</v>
+        <v>-0.2071096129807931</v>
       </c>
       <c r="E59">
-        <v>-0.1746303196922415</v>
+        <v>-0.1746303196922418</v>
       </c>
     </row>
     <row r="60">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.3260637708206611</v>
+        <v>0.3260637708206612</v>
       </c>
       <c r="D60">
-        <v>0.1158956460204551</v>
+        <v>0.1158956460204555</v>
       </c>
       <c r="E60">
-        <v>-0.03723263224000018</v>
+        <v>-0.03723263224000046</v>
       </c>
     </row>
     <row r="61">
@@ -1632,13 +1632,13 @@
         </is>
       </c>
       <c r="C61">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D61">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E61">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="62">
@@ -1653,13 +1653,13 @@
         </is>
       </c>
       <c r="C62">
-        <v>0.638789719885927</v>
+        <v>0.6387897198859274</v>
       </c>
       <c r="D62">
-        <v>0.7547876513668359</v>
+        <v>0.7547876513668365</v>
       </c>
       <c r="E62">
-        <v>-0.1431059974568704</v>
+        <v>-0.1431059974568705</v>
       </c>
     </row>
     <row r="63">
@@ -1674,13 +1674,13 @@
         </is>
       </c>
       <c r="C63">
-        <v>0.1414815395299349</v>
+        <v>0.1414815395299347</v>
       </c>
       <c r="D63">
         <v>-0.9688875580273602</v>
       </c>
       <c r="E63">
-        <v>0.2693206749586884</v>
+        <v>0.2693206749586879</v>
       </c>
     </row>
     <row r="64">
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.1433587781429398</v>
+        <v>0.14335877814294</v>
       </c>
       <c r="D64">
-        <v>0.100082917039975</v>
+        <v>0.1000829170399755</v>
       </c>
       <c r="E64">
-        <v>-0.2955834511472018</v>
+        <v>-0.295583451147202</v>
       </c>
     </row>
     <row r="65">
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="C65">
-        <v>0.473711381021209</v>
+        <v>0.4737113810212094</v>
       </c>
       <c r="D65">
-        <v>0.9067688871382015</v>
+        <v>0.9067688871382021</v>
       </c>
       <c r="E65">
-        <v>-0.06022291976584383</v>
+        <v>-0.06022291976584404</v>
       </c>
     </row>
     <row r="66">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="C66">
-        <v>0.2435148741180645</v>
+        <v>0.2435148741180646</v>
       </c>
       <c r="D66">
-        <v>0.2017867469180534</v>
+        <v>0.2017867469180538</v>
       </c>
       <c r="E66">
-        <v>0.1474233616151254</v>
+        <v>0.1474233616151251</v>
       </c>
     </row>
     <row r="67">
@@ -1758,13 +1758,13 @@
         </is>
       </c>
       <c r="C67">
-        <v>0.05205981105803889</v>
+        <v>0.05205981105803912</v>
       </c>
       <c r="D67">
-        <v>0.09663155954875925</v>
+        <v>0.09663155954875981</v>
       </c>
       <c r="E67">
-        <v>-0.385824330813578</v>
+        <v>-0.3858243308135781</v>
       </c>
     </row>
     <row r="68">
@@ -1785,7 +1785,7 @@
         <v>-2.204074999965556</v>
       </c>
       <c r="E68">
-        <v>-0.3434620704963825</v>
+        <v>-0.3434620704963828</v>
       </c>
     </row>
     <row r="69">
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="C69">
-        <v>-0.09812558067003599</v>
+        <v>-0.09812558067003607</v>
       </c>
       <c r="D69">
-        <v>-0.7238438269797517</v>
+        <v>-0.7238438269797516</v>
       </c>
       <c r="E69">
-        <v>-0.01975570701402734</v>
+        <v>-0.01975570701402771</v>
       </c>
     </row>
     <row r="70">
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="C70">
-        <v>0.7337138107267316</v>
+        <v>0.7337138107267319</v>
       </c>
       <c r="D70">
-        <v>0.9197830943262154</v>
+        <v>0.9197830943262161</v>
       </c>
       <c r="E70">
-        <v>-0.1018702434622638</v>
+        <v>-0.101870243462264</v>
       </c>
     </row>
     <row r="71">
@@ -1845,7 +1845,7 @@
         <v>-1.614160052469678</v>
       </c>
       <c r="D71">
-        <v>0.6823481850812544</v>
+        <v>0.6823481850812548</v>
       </c>
       <c r="E71">
         <v>0.24634192796449</v>
@@ -1863,13 +1863,13 @@
         </is>
       </c>
       <c r="C72">
-        <v>0.3738204780777481</v>
+        <v>0.3738204780777482</v>
       </c>
       <c r="D72">
-        <v>0.1332744288647301</v>
+        <v>0.1332744288647305</v>
       </c>
       <c r="E72">
-        <v>0.01821023129272644</v>
+        <v>0.01821023129272615</v>
       </c>
     </row>
     <row r="73">
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="C73">
-        <v>0.367359869223914</v>
+        <v>0.3673598692239142</v>
       </c>
       <c r="D73">
-        <v>0.1697493177071733</v>
+        <v>0.1697493177071737</v>
       </c>
       <c r="E73">
-        <v>0.1408287905251678</v>
+        <v>0.1408287905251675</v>
       </c>
     </row>
     <row r="74">
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.353599314212153</v>
+        <v>0.3535993142121531</v>
       </c>
       <c r="D74">
-        <v>0.1733090320639378</v>
+        <v>0.1733090320639381</v>
       </c>
       <c r="E74">
-        <v>0.1415615206462741</v>
+        <v>0.1415615206462738</v>
       </c>
     </row>
     <row r="75">
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="C75">
-        <v>-0.128020111199484</v>
+        <v>-0.1280201111994839</v>
       </c>
       <c r="D75">
-        <v>0.2978990345506936</v>
+        <v>0.297899034550694</v>
       </c>
       <c r="E75">
-        <v>0.1672070748849983</v>
+        <v>0.1672070748849981</v>
       </c>
     </row>
     <row r="76">
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="C76">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D76">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E76">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="77">
@@ -1971,10 +1971,10 @@
         <v>0.4636837543062415</v>
       </c>
       <c r="D77">
-        <v>0.1448313172098222</v>
+        <v>0.1448313172098225</v>
       </c>
       <c r="E77">
-        <v>0.135699679677423</v>
+        <v>0.1356996796774226</v>
       </c>
     </row>
     <row r="78">
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.5044458801914846</v>
+        <v>0.5044458801914848</v>
       </c>
       <c r="D78">
-        <v>0.4909298127463931</v>
+        <v>0.4909298127463935</v>
       </c>
       <c r="E78">
-        <v>-0.02320148452344937</v>
+        <v>-0.02320148452344964</v>
       </c>
     </row>
     <row r="79">
@@ -2010,13 +2010,13 @@
         </is>
       </c>
       <c r="C79">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D79">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E79">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="80">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="C80">
-        <v>0.2985570941651087</v>
+        <v>0.2985570941651089</v>
       </c>
       <c r="D80">
-        <v>0.1875478894909956</v>
+        <v>0.1875478894909959</v>
       </c>
       <c r="E80">
-        <v>0.1444924411306998</v>
+        <v>0.1444924411306995</v>
       </c>
     </row>
     <row r="81">
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="C81">
-        <v>0.3948809792474361</v>
+        <v>0.3948809792474363</v>
       </c>
       <c r="D81">
-        <v>0.1626298889936444</v>
+        <v>0.1626298889936448</v>
       </c>
       <c r="E81">
-        <v>0.1393633302829549</v>
+        <v>0.1393633302829546</v>
       </c>
     </row>
     <row r="82">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.131522147924238</v>
+        <v>0.1315221479242384</v>
       </c>
       <c r="D82">
-        <v>1.103849954663943</v>
+        <v>1.103849954663944</v>
       </c>
       <c r="E82">
-        <v>-0.04788465051463122</v>
+        <v>-0.04788465051463128</v>
       </c>
     </row>
     <row r="83">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="C83">
-        <v>-0.03597342819081414</v>
+        <v>-0.03597342819081401</v>
       </c>
       <c r="D83">
-        <v>0.067877347608804</v>
+        <v>0.06787734760880444</v>
       </c>
       <c r="E83">
-        <v>-0.1129168127280602</v>
+        <v>-0.1129168127280604</v>
       </c>
     </row>
     <row r="84">
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="C84">
-        <v>0.5762035661695518</v>
+        <v>0.5762035661695522</v>
       </c>
       <c r="D84">
-        <v>0.9477115853182854</v>
+        <v>0.947711585318286</v>
       </c>
       <c r="E84">
-        <v>-0.0610585423124036</v>
+        <v>-0.06105854231240382</v>
       </c>
     </row>
     <row r="85">
@@ -2136,13 +2136,13 @@
         </is>
       </c>
       <c r="C85">
-        <v>0.2487374097088023</v>
+        <v>0.2487374097088026</v>
       </c>
       <c r="D85">
-        <v>0.7258610920798331</v>
+        <v>0.7258610920798337</v>
       </c>
       <c r="E85">
-        <v>-0.1911767692042712</v>
+        <v>-0.1911767692042713</v>
       </c>
     </row>
     <row r="86">
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="C86">
-        <v>0.5382852752827714</v>
+        <v>0.5382852752827718</v>
       </c>
       <c r="D86">
-        <v>0.7931312924000331</v>
+        <v>0.7931312924000338</v>
       </c>
       <c r="E86">
-        <v>-0.26479103089894</v>
+        <v>-0.2647910308989401</v>
       </c>
     </row>
     <row r="87">
@@ -2178,13 +2178,13 @@
         </is>
       </c>
       <c r="C87">
-        <v>0.367359869223914</v>
+        <v>0.3673598692239142</v>
       </c>
       <c r="D87">
-        <v>0.1697493177071733</v>
+        <v>0.1697493177071737</v>
       </c>
       <c r="E87">
-        <v>0.1408287905251678</v>
+        <v>0.1408287905251675</v>
       </c>
     </row>
     <row r="88">
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="C88">
-        <v>0.5968606826306222</v>
+        <v>0.5968606826306226</v>
       </c>
       <c r="D88">
-        <v>0.7963404912296818</v>
+        <v>0.7963404912296825</v>
       </c>
       <c r="E88">
-        <v>-0.1414336413925351</v>
+        <v>-0.1414336413925353</v>
       </c>
     </row>
     <row r="89">
@@ -2223,10 +2223,10 @@
         <v>-0.2189404855507093</v>
       </c>
       <c r="D89">
-        <v>-0.1159718242786153</v>
+        <v>-0.115971824278615</v>
       </c>
       <c r="E89">
-        <v>0.2619694063724634</v>
+        <v>0.2619694063724631</v>
       </c>
     </row>
     <row r="90">
@@ -2241,13 +2241,13 @@
         </is>
       </c>
       <c r="C90">
-        <v>0.2435148741180645</v>
+        <v>0.2435148741180646</v>
       </c>
       <c r="D90">
-        <v>0.2017867469180534</v>
+        <v>0.2017867469180538</v>
       </c>
       <c r="E90">
-        <v>0.1474233616151254</v>
+        <v>0.1474233616151251</v>
       </c>
     </row>
     <row r="91">
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="C91">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D91">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E91">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="92">
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.6203807735558575</v>
+        <v>0.6203807735558577</v>
       </c>
       <c r="D92">
-        <v>0.9754537122853357</v>
+        <v>0.9754537122853364</v>
       </c>
       <c r="E92">
-        <v>-0.08070871199348863</v>
+        <v>-0.08070871199348881</v>
       </c>
     </row>
     <row r="93">
@@ -2307,10 +2307,10 @@
         <v>-0.2174279229439091</v>
       </c>
       <c r="D93">
-        <v>-0.5810278644885609</v>
+        <v>-0.5810278644885606</v>
       </c>
       <c r="E93">
-        <v>-0.1003120399345882</v>
+        <v>-0.1003120399345884</v>
       </c>
     </row>
     <row r="94">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="C94">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D94">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E94">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="95">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="C95">
-        <v>-0.4169917664464663</v>
+        <v>-0.4169917664464661</v>
       </c>
       <c r="D95">
-        <v>0.3726530360427471</v>
+        <v>0.3726530360427475</v>
       </c>
       <c r="E95">
-        <v>0.1825944074282328</v>
+        <v>0.1825944074282326</v>
       </c>
     </row>
     <row r="96">
@@ -2367,13 +2367,13 @@
         </is>
       </c>
       <c r="C96">
-        <v>0.2501779213591779</v>
+        <v>0.2501779213591778</v>
       </c>
       <c r="D96">
-        <v>-0.6802762485669867</v>
+        <v>-0.6802762485669868</v>
       </c>
       <c r="E96">
-        <v>0.2918948368373448</v>
+        <v>0.2918948368373444</v>
       </c>
     </row>
     <row r="97">
@@ -2388,13 +2388,13 @@
         </is>
       </c>
       <c r="C97">
-        <v>0.426189622690141</v>
+        <v>0.4261896226901413</v>
       </c>
       <c r="D97">
-        <v>0.487971506325351</v>
+        <v>0.4879715063253515</v>
       </c>
       <c r="E97">
-        <v>-0.1005508099517718</v>
+        <v>-0.1005508099517721</v>
       </c>
     </row>
     <row r="98">
@@ -2409,13 +2409,13 @@
         </is>
       </c>
       <c r="C98">
-        <v>0.3260782041886309</v>
+        <v>0.326078204188631</v>
       </c>
       <c r="D98">
-        <v>0.1804284607774667</v>
+        <v>0.180428460777467</v>
       </c>
       <c r="E98">
-        <v>0.143026980888487</v>
+        <v>0.1430269808884867</v>
       </c>
     </row>
     <row r="99">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="C99">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D99">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E99">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="100">
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.5049654193415246</v>
+        <v>0.5049654193415247</v>
       </c>
       <c r="D100">
-        <v>0.1341521741395288</v>
+        <v>0.1341521741395292</v>
       </c>
       <c r="E100">
-        <v>0.1335014893141037</v>
+        <v>0.1335014893141034</v>
       </c>
     </row>
     <row r="101">
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="C101">
-        <v>-0.05438977800990836</v>
+        <v>-0.05438977800990806</v>
       </c>
       <c r="D101">
-        <v>0.2767528768591231</v>
+        <v>0.2767528768591239</v>
       </c>
       <c r="E101">
         <v>-0.5721820705261088</v>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.3174220789678633</v>
+        <v>0.3174220789678636</v>
       </c>
       <c r="D102">
-        <v>0.3722580954697837</v>
+        <v>0.3722580954697842</v>
       </c>
       <c r="E102">
-        <v>-0.1818777352808464</v>
+        <v>-0.1818777352808466</v>
       </c>
     </row>
     <row r="103">
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="C103">
-        <v>0.4451284667772227</v>
+        <v>0.445128466777223</v>
       </c>
       <c r="D103">
-        <v>0.4371410475985864</v>
+        <v>0.4371410475985869</v>
       </c>
       <c r="E103">
-        <v>-0.1699797477895689</v>
+        <v>-0.1699797477895691</v>
       </c>
     </row>
     <row r="104">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="C104">
-        <v>0.4774443093180025</v>
+        <v>0.4774443093180026</v>
       </c>
       <c r="D104">
-        <v>0.1412716028530577</v>
+        <v>0.1412716028530581</v>
       </c>
       <c r="E104">
-        <v>0.1349669495563165</v>
+        <v>0.1349669495563162</v>
       </c>
     </row>
     <row r="105">
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="C105">
-        <v>0.5600076393885688</v>
+        <v>0.5600076393885689</v>
       </c>
       <c r="D105">
-        <v>0.119913316712471</v>
+        <v>0.1199133167124713</v>
       </c>
       <c r="E105">
-        <v>0.1305705688296781</v>
+        <v>0.1305705688296778</v>
       </c>
     </row>
     <row r="106">
@@ -2577,13 +2577,13 @@
         </is>
       </c>
       <c r="C106">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D106">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E106">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="107">
@@ -2598,13 +2598,13 @@
         </is>
       </c>
       <c r="C107">
-        <v>-0.1072420195030233</v>
+        <v>-0.1072420195030238</v>
       </c>
       <c r="D107">
-        <v>-1.789008062155235</v>
+        <v>-1.789008062155236</v>
       </c>
       <c r="E107">
-        <v>0.5523269263319961</v>
+        <v>0.5523269263319955</v>
       </c>
     </row>
     <row r="108">
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.7587041691016718</v>
+        <v>0.7587041691016722</v>
       </c>
       <c r="D108">
-        <v>0.9358038032907532</v>
+        <v>0.9358038032907537</v>
       </c>
       <c r="E108">
-        <v>-0.1016602975637128</v>
+        <v>-0.101660297563713</v>
       </c>
     </row>
     <row r="109">
@@ -2640,13 +2640,13 @@
         </is>
       </c>
       <c r="C109">
-        <v>-0.9586480296360002</v>
+        <v>-0.958648029636</v>
       </c>
       <c r="D109">
-        <v>-1.320801211172681</v>
+        <v>-1.32080121117268</v>
       </c>
       <c r="E109">
-        <v>-0.6535160949187453</v>
+        <v>-0.6535160949187455</v>
       </c>
     </row>
     <row r="110">
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="C110">
-        <v>0.7587041691016718</v>
+        <v>0.7587041691016722</v>
       </c>
       <c r="D110">
-        <v>0.9358038032907532</v>
+        <v>0.9358038032907537</v>
       </c>
       <c r="E110">
-        <v>-0.1016602975637128</v>
+        <v>-0.101660297563713</v>
       </c>
     </row>
     <row r="111">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="C111">
-        <v>0.7724647241134329</v>
+        <v>0.7724647241134333</v>
       </c>
       <c r="D111">
-        <v>0.9322440889339887</v>
+        <v>0.9322440889339894</v>
       </c>
       <c r="E111">
-        <v>-0.1023930276848192</v>
+        <v>-0.1023930276848194</v>
       </c>
     </row>
     <row r="112">
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.9949350769404307</v>
+        <v>-0.9949350769404306</v>
       </c>
       <c r="D113">
-        <v>0.5221610390268541</v>
+        <v>0.5221610390268545</v>
       </c>
       <c r="E113">
-        <v>0.2133690725147018</v>
+        <v>0.2133690725147016</v>
       </c>
     </row>
     <row r="114">
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="C114">
-        <v>0.5183003803647827</v>
+        <v>0.5183003803647829</v>
       </c>
       <c r="D114">
-        <v>0.7685421914707598</v>
+        <v>0.7685421914707603</v>
       </c>
       <c r="E114">
-        <v>-0.0739420572923874</v>
+        <v>-0.07394205729238756</v>
       </c>
     </row>
     <row r="115">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="C115">
-        <v>0.2022332090827813</v>
+        <v>0.2022332090827814</v>
       </c>
       <c r="D115">
-        <v>0.2124658899883468</v>
+        <v>0.2124658899883471</v>
       </c>
       <c r="E115">
-        <v>0.1496215519784446</v>
+        <v>0.1496215519784443</v>
       </c>
     </row>
     <row r="116">
@@ -2787,13 +2787,13 @@
         </is>
       </c>
       <c r="C116">
-        <v>-0.5938890029552614</v>
+        <v>-0.5938890029552619</v>
       </c>
       <c r="D116">
         <v>-2.309638489360102</v>
       </c>
       <c r="E116">
-        <v>0.5685770492724289</v>
+        <v>0.5685770492724284</v>
       </c>
     </row>
     <row r="117">
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="C117">
-        <v>0.4774443093180025</v>
+        <v>0.4774443093180026</v>
       </c>
       <c r="D117">
-        <v>0.1412716028530577</v>
+        <v>0.1412716028530581</v>
       </c>
       <c r="E117">
-        <v>0.1349669495563165</v>
+        <v>0.1349669495563162</v>
       </c>
     </row>
     <row r="118">
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="C118">
-        <v>0.5049654193415246</v>
+        <v>0.5049654193415247</v>
       </c>
       <c r="D118">
-        <v>0.1341521741395288</v>
+        <v>0.1341521741395292</v>
       </c>
       <c r="E118">
-        <v>0.1335014893141037</v>
+        <v>0.1335014893141034</v>
       </c>
     </row>
     <row r="119">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="C119">
-        <v>0.4175631102382835</v>
+        <v>0.4175631102382837</v>
       </c>
       <c r="D119">
-        <v>-0.1270846132196646</v>
+        <v>-0.1270846132196644</v>
       </c>
       <c r="E119">
-        <v>0.1013896355553498</v>
+        <v>0.1013896355553495</v>
       </c>
     </row>
     <row r="120">
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="C120">
-        <v>0.7724647241134329</v>
+        <v>0.7724647241134333</v>
       </c>
       <c r="D120">
-        <v>0.9322440889339887</v>
+        <v>0.9322440889339894</v>
       </c>
       <c r="E120">
-        <v>-0.1023930276848192</v>
+        <v>-0.1023930276848194</v>
       </c>
     </row>
     <row r="121">
@@ -2892,13 +2892,13 @@
         </is>
       </c>
       <c r="C121">
-        <v>0.3738204780777481</v>
+        <v>0.3738204780777482</v>
       </c>
       <c r="D121">
-        <v>0.1332744288647301</v>
+        <v>0.1332744288647305</v>
       </c>
       <c r="E121">
-        <v>0.01821023129272644</v>
+        <v>0.01821023129272615</v>
       </c>
     </row>
     <row r="122">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="C122">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D122">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E122">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="123">
@@ -2934,13 +2934,13 @@
         </is>
       </c>
       <c r="C123">
-        <v>0.3726307834391843</v>
+        <v>0.3726307834391844</v>
       </c>
       <c r="D123">
-        <v>0.06685577257820982</v>
+        <v>0.0668557725782102</v>
       </c>
       <c r="E123">
-        <v>-0.03025797074556076</v>
+        <v>-0.03025797074556105</v>
       </c>
     </row>
     <row r="124">
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="C124">
-        <v>0.5737681944003299</v>
+        <v>0.57376819440033</v>
       </c>
       <c r="D124">
-        <v>0.1163536023557066</v>
+        <v>0.1163536023557069</v>
       </c>
       <c r="E124">
-        <v>0.1298378387085717</v>
+        <v>0.1298378387085714</v>
       </c>
     </row>
     <row r="125">
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="C125">
-        <v>-0.7566355851344139</v>
+        <v>-0.7566355851344145</v>
       </c>
       <c r="D125">
-        <v>-2.333803434476308</v>
+        <v>-2.333803434476309</v>
       </c>
       <c r="E125">
-        <v>0.7472090969108425</v>
+        <v>0.7472090969108418</v>
       </c>
     </row>
     <row r="126">
@@ -3000,10 +3000,10 @@
         <v>-11.83825242620814</v>
       </c>
       <c r="D126">
-        <v>3.327215952157242</v>
+        <v>3.327215952157244</v>
       </c>
       <c r="E126">
-        <v>0.7907604079465481</v>
+        <v>0.7907604079465506</v>
       </c>
     </row>
   </sheetData>
